--- a/private/siradig.xlsx
+++ b/private/siradig.xlsx
@@ -526,7 +526,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>3. Pestaña 'Parámetros': escala y deducciones personales de ARCA 2026 (acumulado a diciembre) y los topes que debés completar (hipotecario, seguro de vida).</t>
+          <t>3. Pestaña 'Parámetros': escala y deducciones personales de ARCA 2026 (acumulado a diciembre) y los topes de ARCA para intereses hipotecarios ($20.000 al año) y seguro de vida ($753.472,14 en 2026).</t>
         </is>
       </c>
     </row>
@@ -574,7 +574,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Intereses hipotecarios y seguro de vida: completá el tope anual en 'Parámetros' (si queda vacío, no se aplica tope y la hoja avisa).</t>
+          <t>Intereses hipotecarios y seguro de vida: tope anual en 'Parámetros' ($20.000 y $753.472,14 en 2026, según ARCA). Actualizalo cada año.</t>
         </is>
       </c>
     </row>
@@ -672,15 +672,19 @@
           <t>Tope anual intereses hipotecarios</t>
         </is>
       </c>
-      <c r="B8" s="4" t="n"/>
+      <c r="B8" s="4" t="n">
+        <v>20000</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Tope anual seguro de vida</t>
-        </is>
-      </c>
-      <c r="B9" s="4" t="n"/>
+          <t>Tope anual seguro de vida (2026)</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n">
+        <v>753472.14</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -3135,7 +3139,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>El cierre del plazo de carga es en marzo del año siguiente: confirmá la fecha exacta en ARCA.</t>
+          <t>El plazo de carga vence el 31 de marzo del año siguiente (ARCA). Si ARCA lo prorroga, rige la nueva fecha.</t>
         </is>
       </c>
     </row>
